--- a/Result/checksun_type/幹細胞開發.xlsx
+++ b/Result/checksun_type/幹細胞開發.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>27.0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>27.32</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>28.96</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>6377966.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>6176987.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>6176987.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>5819335.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>7057711.28</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>7057711.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>318810.7876168946</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>6377966</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>6377966.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>26.65</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>27.34</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>29.0</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>27.34</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>29</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>14065095.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>5502534.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>5502534.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>5577139.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7141675.4</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7141675.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>354777.3309102692</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>14065095</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>14065095.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>26.32</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>27.38</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>29.06</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2914289.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3848013.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3848013.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>4769960.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7033263.38</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7033263.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-430133.4762031334</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2914289</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2914289.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>26.41</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>27.52</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>29.16</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>29.16</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>4874674.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4326733.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>4326733.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>5162658.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7253837.46</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7253837.46</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-341343.5050721681</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>4874674</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4874674.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>26.76</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>29.27</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>29.27</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>2652914.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4882698.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>4882698.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>5090432.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>7327974.3</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>7327974.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-412351.0997039247</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>2652914</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2652914.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>26.91</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>27.88</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>29.36</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>29.36</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3005699.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>5461683.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>5461683</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>5213400.7</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>7669422.94</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>7669422.94</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-261017.9813312953</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3005699</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3005699.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>27.11</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>29.48</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>29.48</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>5792491.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>5651744.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>5651744.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>5390737.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>7832741.84</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>7832741.84</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-73304.13432285003</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>5792491</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>5792491.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>27.24</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>28.2</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>29.6</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>29.6</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>5307889.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>5691908.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>5691908</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>5278991.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>8214914.5</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>8214914.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-101108.3480849694</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>5307889</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>5307889.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>27.29</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>28.36</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>29.72</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>29.72</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>7654500.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>5998583.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>5998583.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>4953026.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>8631788.52</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>8631788.52</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-85295.99817067571</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>7654500</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>7654500.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>27.27</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>28.44</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>29.8</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>5547836.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>5298166.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>5298166.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>4494096.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>8670075.9</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>8670075.9</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-311083.2483584471</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>5547836</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>5547836.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>27.34</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>28.52</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>29.89</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>29.89</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>3956007.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4965118.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4965118.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>4940124.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>8893843.2</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>8893843.199999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-396812.3468996035</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>3956007</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>3956007.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>74.62</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>70.12</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>75.44</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>75.44</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>11803273.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>5974358.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>5974358</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>4611286.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>5891570.66</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>5891570.66</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>859958.0196654936</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>11803273</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>11803273.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>72.58000000000001</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>69.47</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>75.39</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>69.47</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>75.39</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>8218048.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>4055045.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>4055045.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>3547077.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>5682855.9</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>5682855.9</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>323791.1767962705</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>8218048</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>8218048.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>70.92</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>68.88</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>75.4</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>5892899.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>2922071.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>2922071.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>2881353.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>5559272.96</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>5559272.96</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-69594.17647391511</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>5892899</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>5892899.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>70.53999999999999</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>68.68</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>75.53</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>68.68000000000001</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>75.53</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1574352.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>2303865.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>2303865.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>2493228.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>5477122.58</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>5477122.58</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-379964.6391286822</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1574352</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1574352.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>70.47999999999999</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>68.61</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>75.66</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>68.61</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>75.66</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>2383218.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>2554543.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>2554543.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>2423350.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>5475035.54</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>5475035.54</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-347079.384380897</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>2383218</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2383218.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>70.5</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>68.57</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>75.8</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>68.56999999999999</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>75.8</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>2206711.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>3248215.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>3248215</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>2398454.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>5474171.38</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>5474171.38</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-374368.971013315</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>2206711</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2206711.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>69.78</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>68.56</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>75.95</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>68.56</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>75.95</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>2553178.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>3039109.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>3039109.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>2377470.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>5460980.24</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>5460980.24</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-381072.310094865</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>2553178</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2553178.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>68.96000000000001</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>68.54</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>76.09</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>68.54000000000001</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>76.09</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>2801867.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>2840636.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>2840636.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>2238981.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>5451442.24</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>5451442.24</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-414160.247707977</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>2801867</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2801867.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>68.34</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>68.55</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>76.24</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>76.23999999999999</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>2827743.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>2682591.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>2682591.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>2103125.1</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>5454723.16</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>5454723.16</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-473282.5425942801</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>2827743</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>2827743.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>67.86</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>68.54</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>76.37</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>68.54000000000001</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>76.37</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>5851576.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>2292158.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>2292158.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1923889.0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>5440870.28</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>5440870.28</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-543612.4444820606</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>5851576</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>5851576.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>67.3</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>68.9</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>76.48</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>76.48</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>1161182.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1548693.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1548693.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1818036.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>5348507.92</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>5348507.92</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-948651.1098759589</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>1161182</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1161182.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>168.6</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>163.72</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>167.16</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>163.72</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>167.16</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>39044.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>41837.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>41837.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>38891.0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>1683.46524333056</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>39044</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>39044.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>167.6</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>163.32</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>167.02</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>163.32</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>167.02</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>41554.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>41392.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>41392</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>36289.2</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>2047.507224716806</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>41554</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>41554.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>166.6</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>162.93</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>166.84</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>162.93</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>166.84</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>83550.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>42576.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>42576</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>34618.0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>2225.513368671556</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>83550</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>83550.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>165.4</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>162.55</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>166.67</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>162.55</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>166.67</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>20153.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>32663.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>32663.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>29235.5</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-2099.246188845646</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>20153</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>20153.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>165.4</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>162.48</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>166.56</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>162.48</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>166.56</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>24885.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>34878.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>34878.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>30090.8</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-1409.96533569715</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>24885</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>24885.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>164.9</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>162.52</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>166.41</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>162.52</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>166.41</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>36818.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>35944.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>35944.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>28638.5</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-881.9224977815466</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>36818</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>36818.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>164.2</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>162.65</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>166.25</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>162.65</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>166.25</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>47474.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>31186.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>31186.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>27910.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-1374.614068695628</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>47474</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>47474.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>163.0</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>162.65</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>166.09</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>162.65</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>166.09</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>33988.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>26660.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>26660</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>29079.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-3171.080096119476</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>33988</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>33988.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>161.7</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>162.62</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>165.94</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>162.62</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>165.94</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>31229.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>25807.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>25807.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>27476.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>0</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-4179.278703292122</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>31229</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>31229.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>160.6</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>162.55</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>165.76</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>162.55</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>165.76</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>30215.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>25302.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>25302.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>26355.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-5174.695331278326</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>30215</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>30215.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>160.3</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>162.57</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>165.63</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>162.57</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>165.63</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>13026.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>21332.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>21332.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>26480.0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-6303.265680855824</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>13026</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>13026.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>14.67</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>16.85</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>1877.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>1612.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>1612.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>1484.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>2404.96</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>2404.96</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-218.5414979881389</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>1877</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>1877.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>14.69</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>15.54</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>16.91</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>16.91</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>1133.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>1407.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>1407.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>1535.1</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>2509.52</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>2509.52</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-260.0078192599899</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>1133</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>1133.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>14.77</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>15.65</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>17</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>2840.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>1448.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>1448.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>1659.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>2535.26</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>2535.26</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-230.2451418176345</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>2840</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>2840.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>14.88</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>15.79</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>17.09</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>17.09</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>1469.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>1343.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>1343.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>2211.1</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>2531.16</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>2531.16</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-362.3968475493537</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>1469</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>1469.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>15.05</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>15.94</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>17.18</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>17.18</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>742.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>1287.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>1287.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>2279.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>2582.94</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>2582.94</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-391.3493968964758</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>742</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>742.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>15.14</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>16.06</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>17.26</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>17.26</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>852.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>1357.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>1357.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>2336.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>2620.3</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>2620.3</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-340.8405603603476</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>852</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>852.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>15.33</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>16.18</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>17.34</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>17.34</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>1339.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>1663.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>1663</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>2457.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>2719.2</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>2719.2</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-268.297916724438</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>1339</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>1339.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>15.42</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>17.43</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>17.43</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>2315.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>1870.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>1870.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>2981.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>2774.36</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>2774.36</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-207.2620716472657</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>2315</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>2315.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>15.44</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>16.44</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>17.52</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>17.52</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>1190.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>3078.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>3078.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>2915.3</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>2807.38</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>2807.38</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-217.2372189781881</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>1190</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>1190.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>15.56</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>16.57</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>17.59</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>17.59</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>1092.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>3271.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>3271.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>2994.1</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>2855.18</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>2855.18</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-103.1932430588572</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>1092</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>1092.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>15.68</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>16.69</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>17.67</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>17.67</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>2379.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>3316.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>3316</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>3207.2</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>2889.22</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>2889.22</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>73.91219550657479</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>2379</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>2379.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>93.2</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>97.23</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>88.79</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>97.23</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>88.79000000000001</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>42037.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>25842.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>25842.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>56552.8</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>67934.28</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>67934.28</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-12135.08012647409</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>42037</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>42037.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>92.52</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>97.38</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>88.56</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>97.38</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>88.56</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>12382.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>38343.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>38343.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>56557.5</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>68309.54</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>68309.53999999999</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-13508.89251978778</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>12382</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>12382.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>93.7</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>97.24</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>88.43</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>97.23999999999999</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>88.43000000000001</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>16189.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>48240.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>48240.6</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>58792.3</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>69435.04</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>69435.03999999999</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-11811.69977738634</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>16189</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>16189.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>95.17999999999999</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>97.23</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>88.33</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>97.23</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>88.33</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>25530.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>57684.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>57684.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>62660.2</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>71866.54</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>71866.53999999999</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-9373.185153334773</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>25530</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>25530.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>97.4</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>97.24</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>88.22</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>97.23999999999999</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>88.22</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>33074.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>79687.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>79687</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>67828.1</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>73665.88</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>73665.88</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-6555.657649213419</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>33074</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>33074.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>98.49999999999999</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>97.14</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>87.93</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>87.93000000000001</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>104544.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>87263.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>87263.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>71316.0</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>74110.96</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>74110.96000000001</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-3104.773441568163</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>104544</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>104544.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>98.88</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>96.76</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>87.62</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>96.76000000000001</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>87.62</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>61866.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>74771.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>74771.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>69626.9</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>72209.06</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>72209.06</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-5721.554093447514</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>61866</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>61866.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>97.88000000000001</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>96.01</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>87.2</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>96.01000000000001</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>87.2</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>63409.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>69344.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>69344</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>71704.0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>71598.78</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>71598.78</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-4682.828092794865</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>63409</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>63409.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>96.7</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>95.31</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>86.75</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>86.75</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>135542.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>67635.8</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>67635.8</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>79409.8</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>70847.3</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>70847.3</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-3197.0113742627</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>135542</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>135542.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>95.24</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>94.24</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>86.23</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>94.23999999999999</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>86.23</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>70955.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>55969.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>55969.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>91411.3</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>68593.44</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>68593.44</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-8688.772798707374</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>70955</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>70955.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>95.35999999999999</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>93.3</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>85.78</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>85.78</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>42084.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>55368.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>55368.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>120243.6</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>67557.38</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>67557.38</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-9303.7972336745</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>42084</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>42084.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
